--- a/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49571</t>
+          <t>49327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55222</t>
+          <t>55230</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43715</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50012</t>
+          <t>49502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95792</t>
+          <t>95470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103927</t>
+          <t>104197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>301130</t>
+          <t>300607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307876</t>
+          <t>307880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342106</t>
+          <t>342038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350247</t>
+          <t>350414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646071</t>
+          <t>645889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657068</t>
+          <t>656838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129643</t>
+          <t>129455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135731</t>
+          <t>135730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115174</t>
+          <t>115230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122046</t>
+          <t>122135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>247756</t>
+          <t>248355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>256765</t>
+          <t>257070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486025</t>
+          <t>486122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>496564</t>
+          <t>497056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>507201</t>
+          <t>507912</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>519564</t>
+          <t>519367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>997510</t>
+          <t>996915</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1013923</t>
+          <t>1013796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59884</t>
+          <t>59671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115398</t>
+          <t>115406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>25143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>287092</t>
+          <t>286416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>297823</t>
+          <t>297610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329575</t>
+          <t>328722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337082</t>
+          <t>337314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>619926</t>
+          <t>619303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>633450</t>
+          <t>633333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110106</t>
+          <t>109216</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116077</t>
+          <t>116073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131832</t>
+          <t>132060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244523</t>
+          <t>244567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252283</t>
+          <t>252281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>30036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>455118</t>
+          <t>454921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>467943</t>
+          <t>468177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>525702</t>
+          <t>526059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>534764</t>
+          <t>534828</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>985727</t>
+          <t>985710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1001101</t>
+          <t>1001245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33838</t>
+          <t>33410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39436</t>
+          <t>39408</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47257</t>
+          <t>46949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82757</t>
+          <t>82915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90011</t>
+          <t>89937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26942</t>
+          <t>27316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29536</t>
+          <t>29108</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>48854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>321328</t>
+          <t>321237</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335515</t>
+          <t>335760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352924</t>
+          <t>352550</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367038</t>
+          <t>366264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>679079</t>
+          <t>679734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>699052</t>
+          <t>699480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17268</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128333</t>
+          <t>128314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134681</t>
+          <t>134709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127804</t>
+          <t>127613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136881</t>
+          <t>136675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258689</t>
+          <t>258799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270378</t>
+          <t>270130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36715</t>
+          <t>37235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65880</t>
+          <t>65626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>490117</t>
+          <t>489714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>506655</t>
+          <t>505839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>534318</t>
+          <t>533798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>551515</t>
+          <t>551049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1030543</t>
+          <t>1030797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1053714</t>
+          <t>1054838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45067</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52803</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51354</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59687</t>
+          <t>59349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99901</t>
+          <t>100580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110702</t>
+          <t>110951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20635</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38853</t>
+          <t>39291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>45772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49819</t>
+          <t>49217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76945</t>
+          <t>78032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>421657</t>
+          <t>421219</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439875</t>
+          <t>440153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469993</t>
+          <t>470847</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491457</t>
+          <t>491744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>900184</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927310</t>
+          <t>927912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143732</t>
+          <t>143972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148804</t>
+          <t>148854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173544</t>
+          <t>173707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181680</t>
+          <t>181823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320594</t>
+          <t>320007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329482</t>
+          <t>329027</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>26767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46468</t>
+          <t>46786</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55711</t>
+          <t>56348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>65836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95537</t>
+          <t>96455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>618270</t>
+          <t>617952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>637879</t>
+          <t>637971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706261</t>
+          <t>705624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>728902</t>
+          <t>728404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1331173</t>
+          <t>1330255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1361510</t>
+          <t>1360874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3997</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3198</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7135</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7168</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3997</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1869</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8371</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47374</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43269</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49560</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53264</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49327</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55230</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49294</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55208</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>47374</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>43000</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>49502</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95470</t>
+          <t>95916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104197</t>
+          <t>103919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6509</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3315</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11644</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5078</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2437</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9710</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9579</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,64%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6509</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3222</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11598</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>347127</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>341992</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>350321</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>305239</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>300607</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>307880</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>300738</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>307834</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,36%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>347127</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>342038</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>350414</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>645889</t>
+          <t>646748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656838</t>
+          <t>657286</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3943</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8690</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2723</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7126</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6934</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3943</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1407</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8312</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>12646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>119599</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114852</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>122098</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>133858</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>129455</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>135730</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>129647</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>135907</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,01%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>119599</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>115230</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>122135</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248355</t>
+          <t>247477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257070</t>
+          <t>256709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9318</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21718</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6303</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17237</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6875</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17028</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14449</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9182</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20637</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>34190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>514100</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>506831</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>519231</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>729</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>492359</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>486122</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>497056</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>486331</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>496484</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>514100</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>507912</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>519367</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>996915</t>
+          <t>997718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1013796</t>
+          <t>1013689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,107 +2326,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>429</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2419</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61661</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59955</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61661</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>59671</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115406</t>
+          <t>115637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5576</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10737</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11301</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7043</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18237</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6680</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18189</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5576</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2479</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11071</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25143</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>334217</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>329056</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>337132</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>425</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>293352</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>286416</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>297610</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>286464</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>297973</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>334217</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>328722</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>337314</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>619303</t>
+          <t>619756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>633333</t>
+          <t>633534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4923</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2884</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7611</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7291</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,47%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4838</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>135502</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>131975</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>113943</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>109216</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>116073</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>109536</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>116066</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,53%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,76%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>135502</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>132060</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>353</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244567</t>
+          <t>245041</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252281</t>
+          <t>252215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12897</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>14185</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8788</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22044</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9196</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21670</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12722</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>30955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>531381</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>525884</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>535198</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>667</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>462780</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>454921</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>468177</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>455295</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>467769</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>531381</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>526059</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>534828</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>985710</t>
+          <t>984791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1001245</t>
+          <t>1000311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3325</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7231</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1238</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,18%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4288</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49939</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46747</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>37316</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33410</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39408</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>33531</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>39403</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,82%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>49939</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>46949</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82915</t>
+          <t>82678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89937</t>
+          <t>90020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19247</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13012</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26982</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19148</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12962</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27485</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13469</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26895</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19247</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13602</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27316</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29108</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48854</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>360619</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>352884</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>366854</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>496</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>329574</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>321237</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>335760</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>321827</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>335253</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>360619</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>352550</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>366264</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>679734</t>
+          <t>678173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>699480</t>
+          <t>698356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6542</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12049</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3816</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1318</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7713</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6542</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12317</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>133388</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>127881</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>137038</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>132211</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>128314</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134709</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>128234</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>134738</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,19%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>133388</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>127613</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>136675</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258799</t>
+          <t>259776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270130</t>
+          <t>270151</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4963,67 +4963,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20042</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36656</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>26289</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19551</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35676</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19342</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35472</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>27087</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19984</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>37235</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65626</t>
+          <t>66358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>543946</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>534377</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>550991</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>499101</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>489714</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>505839</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>489918</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>506048</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>543946</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>533798</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>551049</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1030797</t>
+          <t>1030065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1054838</t>
+          <t>1053087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5379</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10119</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4713</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1645</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9188</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51353</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46613</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54224</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>49965</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45490</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53033</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56522</t>
+          <t>42006</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>44706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>106488</t>
+          <t>93359</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100580</t>
+          <t>87309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110951</t>
+          <t>97731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23981</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44212</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28910</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20357</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>39291</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33920</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24875</t>
+          <t>21424</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45772</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>62831</t>
+          <t>63136</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49217</t>
+          <t>51604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78032</t>
+          <t>80338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>442486</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>431466</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>451697</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>600</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>431600</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>421219</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>440153</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>482699</t>
+          <t>402504</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470847</t>
+          <t>393798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491744</t>
+          <t>411024</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>914298</t>
+          <t>844990</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>899097</t>
+          <t>827788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927912</t>
+          <t>856522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1566</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8337</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5579</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>782</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>164662</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>160082</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166853</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>147112</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>143972</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148854</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>178896</t>
+          <t>147354</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173707</t>
+          <t>144176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181823</t>
+          <t>149194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>326009</t>
+          <t>312016</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320007</t>
+          <t>307504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329027</t>
+          <t>315421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42328</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31498</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>55840</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>36061</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26767</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>46786</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56348</t>
+          <t>47225</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>79646</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65836</t>
+          <t>65267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96455</t>
+          <t>94991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>658501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>644989</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>669331</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>887</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>628677</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>617952</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>637971</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>917</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>718117</t>
+          <t>591863</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>705624</t>
+          <t>581957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>728404</t>
+          <t>601685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1346794</t>
+          <t>1250365</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1330255</t>
+          <t>1235020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1360874</t>
+          <t>1264744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
